--- a/artfynd/A 49560-2024 artfynd.xlsx
+++ b/artfynd/A 49560-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121078807</v>
+        <v>121078554</v>
       </c>
       <c r="B2" t="n">
-        <v>98071</v>
+        <v>98081</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507467</v>
+        <v>507434</v>
       </c>
       <c r="R2" t="n">
-        <v>6985357</v>
+        <v>6985353</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121099245</v>
+        <v>121078807</v>
       </c>
       <c r="B3" t="n">
-        <v>78599</v>
+        <v>98081</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,44 +808,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>230405</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Middagsberget, Jmt</t>
+          <t>Middagsberget, Middagsberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507503</v>
+        <v>507467</v>
       </c>
       <c r="R3" t="n">
         <v>6985357</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,18 +878,27 @@
           <t>2024-11-08</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-08</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -905,7 +920,7 @@
         <v>121080011</v>
       </c>
       <c r="B4" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -1014,10 +1029,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121078554</v>
+        <v>121099245</v>
       </c>
       <c r="B5" t="n">
-        <v>98071</v>
+        <v>78602</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,50 +1041,44 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>230405</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Middagsberget, Middagsberget, Jmt</t>
+          <t>Middagsberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507434</v>
+        <v>507503</v>
       </c>
       <c r="R5" t="n">
-        <v>6985353</v>
+        <v>6985357</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1096,27 +1105,18 @@
           <t>2024-11-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-08</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1138,7 +1138,7 @@
         <v>121078567</v>
       </c>
       <c r="B6" t="n">
-        <v>79679</v>
+        <v>79682</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>

--- a/artfynd/A 49560-2024 artfynd.xlsx
+++ b/artfynd/A 49560-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121078554</v>
+        <v>121080011</v>
       </c>
       <c r="B2" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Middagsberget, Middagsberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507434</v>
+        <v>507426</v>
       </c>
       <c r="R2" t="n">
-        <v>6985353</v>
+        <v>6985423</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121078807</v>
+        <v>121078567</v>
       </c>
       <c r="B3" t="n">
-        <v>98081</v>
+        <v>79682</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,50 +799,41 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Middagsberget, Middagsberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507467</v>
+        <v>507434</v>
       </c>
       <c r="R3" t="n">
-        <v>6985357</v>
+        <v>6985353</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -880,7 +862,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -890,7 +872,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -917,10 +899,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121080011</v>
+        <v>121099245</v>
       </c>
       <c r="B4" t="n">
-        <v>79682</v>
+        <v>78602</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -933,37 +915,40 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Middagsberget, Middagsberget, Jmt</t>
+          <t>Middagsberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507426</v>
+        <v>507503</v>
       </c>
       <c r="R4" t="n">
-        <v>6985423</v>
+        <v>6985357</v>
       </c>
       <c r="S4" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -990,27 +975,18 @@
           <t>2024-11-08</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-08</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1029,10 +1005,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121099245</v>
+        <v>121078807</v>
       </c>
       <c r="B5" t="n">
-        <v>78602</v>
+        <v>98081</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1041,44 +1017,50 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>230405</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Middagsberget, Jmt</t>
+          <t>Middagsberget, Middagsberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507503</v>
+        <v>507467</v>
       </c>
       <c r="R5" t="n">
         <v>6985357</v>
       </c>
       <c r="S5" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1105,18 +1087,27 @@
           <t>2024-11-08</t>
         </is>
       </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-08</t>
         </is>
       </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1135,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121078567</v>
+        <v>121078554</v>
       </c>
       <c r="B6" t="n">
-        <v>79682</v>
+        <v>98081</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,28 +1138,37 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Middagsberget, Middagsberget, Jmt</t>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 49560-2024 artfynd.xlsx
+++ b/artfynd/A 49560-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121080011</v>
+        <v>121078554</v>
       </c>
       <c r="B2" t="n">
-        <v>79682</v>
+        <v>98094</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,41 +687,50 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
           <t>Middagsberget, Middagsberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507426</v>
+        <v>507434</v>
       </c>
       <c r="R2" t="n">
-        <v>6985423</v>
+        <v>6985353</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -750,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -760,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>12:55</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,10 +796,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121078567</v>
+        <v>121099245</v>
       </c>
       <c r="B3" t="n">
-        <v>79682</v>
+        <v>78605</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -803,37 +812,40 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Middagsberget, Middagsberget, Jmt</t>
+          <t>Middagsberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507434</v>
+        <v>507503</v>
       </c>
       <c r="R3" t="n">
-        <v>6985353</v>
+        <v>6985357</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,27 +872,18 @@
           <t>2024-11-08</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-08</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>11:31</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -899,10 +902,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121099245</v>
+        <v>121078567</v>
       </c>
       <c r="B4" t="n">
-        <v>78602</v>
+        <v>79685</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -915,40 +918,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>230405</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Middagsberget, Jmt</t>
+          <t>Middagsberget, Middagsberget, Jmt</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507503</v>
+        <v>507434</v>
       </c>
       <c r="R4" t="n">
-        <v>6985357</v>
+        <v>6985353</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -975,18 +975,27 @@
           <t>2024-11-08</t>
         </is>
       </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-11-08</t>
         </is>
       </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>11:31</t>
+        </is>
+      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1005,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121078807</v>
+        <v>121080011</v>
       </c>
       <c r="B5" t="n">
-        <v>98081</v>
+        <v>79685</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1017,47 +1026,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Middagsberget, Middagsberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507467</v>
+        <v>507426</v>
       </c>
       <c r="R5" t="n">
-        <v>6985357</v>
+        <v>6985423</v>
       </c>
       <c r="S5" t="n">
         <v>20</v>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121078554</v>
+        <v>121078807</v>
       </c>
       <c r="B6" t="n">
-        <v>98081</v>
+        <v>98094</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1175,13 +1175,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507434</v>
+        <v>507467</v>
       </c>
       <c r="R6" t="n">
-        <v>6985353</v>
+        <v>6985357</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 49560-2024 artfynd.xlsx
+++ b/artfynd/A 49560-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121078554</v>
+        <v>121078807</v>
       </c>
       <c r="B2" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -710,7 +710,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>60</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -724,13 +724,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507434</v>
+        <v>507467</v>
       </c>
       <c r="R2" t="n">
-        <v>6985353</v>
+        <v>6985357</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +759,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +769,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:39</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>121078807</v>
+        <v>121078554</v>
       </c>
       <c r="B6" t="n">
-        <v>98094</v>
+        <v>98095</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>50</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1175,13 +1175,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>507467</v>
+        <v>507434</v>
       </c>
       <c r="R6" t="n">
-        <v>6985357</v>
+        <v>6985353</v>
       </c>
       <c r="S6" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1210,7 +1210,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD6" t="b">

--- a/artfynd/A 49560-2024 artfynd.xlsx
+++ b/artfynd/A 49560-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121078807</v>
+        <v>121078567</v>
       </c>
       <c r="B2" t="n">
-        <v>98095</v>
+        <v>79688</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,50 +687,41 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Middagsberget, Middagsberget, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>507467</v>
+        <v>507434</v>
       </c>
       <c r="R2" t="n">
-        <v>6985357</v>
+        <v>6985353</v>
       </c>
       <c r="S2" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -759,7 +750,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -769,7 +760,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>11:39</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -796,10 +787,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121099245</v>
+        <v>121078807</v>
       </c>
       <c r="B3" t="n">
-        <v>78605</v>
+        <v>98098</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -808,44 +799,50 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>230405</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav (ssp. sarmentosa)</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa subsp. sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Middagsberget, Jmt</t>
+          <t>Middagsberget, Middagsberget, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>507503</v>
+        <v>507467</v>
       </c>
       <c r="R3" t="n">
         <v>6985357</v>
       </c>
       <c r="S3" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -872,18 +869,27 @@
           <t>2024-11-08</t>
         </is>
       </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-11-08</t>
         </is>
       </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>11:39</t>
+        </is>
+      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -902,10 +908,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121078567</v>
+        <v>121080011</v>
       </c>
       <c r="B4" t="n">
-        <v>79685</v>
+        <v>79688</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -942,13 +948,13 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>507434</v>
+        <v>507426</v>
       </c>
       <c r="R4" t="n">
-        <v>6985353</v>
+        <v>6985423</v>
       </c>
       <c r="S4" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -977,7 +983,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -987,7 +993,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>12:55</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1014,10 +1020,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>121080011</v>
+        <v>121099245</v>
       </c>
       <c r="B5" t="n">
-        <v>79685</v>
+        <v>78608</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,37 +1036,40 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>230405</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav (ssp. sarmentosa)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa subsp. sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Middagsberget, Middagsberget, Jmt</t>
+          <t>Middagsberget, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>507426</v>
+        <v>507503</v>
       </c>
       <c r="R5" t="n">
-        <v>6985423</v>
+        <v>6985357</v>
       </c>
       <c r="S5" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1087,27 +1096,18 @@
           <t>2024-11-08</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-11-08</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>12:55</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1129,7 +1129,7 @@
         <v>121078554</v>
       </c>
       <c r="B6" t="n">
-        <v>98095</v>
+        <v>98098</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
